--- a/Excel/Vertical/perbandingan_Waktu Pencarian.xlsx
+++ b/Excel/Vertical/perbandingan_Waktu Pencarian.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SEMHAS\TA_Python_Server\Excel\Vertical\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62052063-8014-45E7-9F95-A0E1DEFE6E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -58,17 +52,17 @@
     <t>Map_4</t>
   </si>
   <si>
+    <t>Naik</t>
+  </si>
+  <si>
     <t>Turun</t>
-  </si>
-  <si>
-    <t>Naik</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -78,13 +72,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -124,41 +111,27 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -196,7 +169,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -230,7 +203,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -265,10 +237,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -441,14 +412,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="6" max="6" width="8.88671875" style="3"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -464,14 +432,14 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -479,22 +447,22 @@
         <v>16</v>
       </c>
       <c r="C2">
-        <v>4.638E-4</v>
+        <v>0.0004396000000000001</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
       </c>
       <c r="E2">
-        <v>4.7540000000000012E-4</v>
-      </c>
-      <c r="F2" s="3">
-        <v>-2.5010780508840279E-2</v>
+        <v>0.0003564</v>
+      </c>
+      <c r="F2">
+        <v>0.1892629663330303</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -502,22 +470,22 @@
         <v>32</v>
       </c>
       <c r="C3">
-        <v>3.3869E-3</v>
+        <v>0.0033719</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
       </c>
       <c r="E3">
-        <v>1.3898999999999999E-3</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0.58962473057958609</v>
+        <v>0.0009503</v>
+      </c>
+      <c r="F3">
+        <v>0.7181707642575403</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -525,22 +493,22 @@
         <v>64</v>
       </c>
       <c r="C4">
-        <v>2.4077600000000001E-2</v>
+        <v>0.0238073</v>
       </c>
       <c r="D4" t="s">
         <v>3</v>
       </c>
       <c r="E4">
-        <v>4.5272999999999997E-3</v>
-      </c>
-      <c r="F4" s="3">
-        <v>0.8119704621723095</v>
+        <v>0.0029309</v>
+      </c>
+      <c r="F4">
+        <v>0.8768907015915286</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -548,22 +516,22 @@
         <v>128</v>
       </c>
       <c r="C5">
-        <v>0.15187539999999999</v>
+        <v>0.156436</v>
       </c>
       <c r="D5" t="s">
         <v>3</v>
       </c>
       <c r="E5">
-        <v>1.7998400000000001E-2</v>
-      </c>
-      <c r="F5" s="3">
-        <v>0.88149232857987536</v>
+        <v>0.0107648</v>
+      </c>
+      <c r="F5">
+        <v>0.9311871947633538</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -571,22 +539,22 @@
         <v>16</v>
       </c>
       <c r="C6">
-        <v>4.7569999999999991E-4</v>
+        <v>0.000488</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
       </c>
       <c r="E6">
-        <v>4.2559999999999999E-4</v>
-      </c>
-      <c r="F6" s="3">
-        <v>0.10531847803237319</v>
+        <v>0.0003851</v>
+      </c>
+      <c r="F6">
+        <v>0.2108606557377049</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -594,22 +562,22 @@
         <v>32</v>
       </c>
       <c r="C7">
-        <v>2.8988E-3</v>
+        <v>0.002934</v>
       </c>
       <c r="D7" t="s">
         <v>8</v>
       </c>
       <c r="E7">
-        <v>1.4189000000000001E-3</v>
-      </c>
-      <c r="F7" s="3">
-        <v>0.5105215951428177</v>
+        <v>0.0010217</v>
+      </c>
+      <c r="F7">
+        <v>0.651772324471711</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -617,22 +585,22 @@
         <v>64</v>
       </c>
       <c r="C8">
-        <v>1.8620899999999999E-2</v>
+        <v>0.0191111</v>
       </c>
       <c r="D8" t="s">
         <v>8</v>
       </c>
       <c r="E8">
-        <v>3.7632999999999998E-3</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0.79789913484310637</v>
+        <v>0.0027238</v>
+      </c>
+      <c r="F8">
+        <v>0.8574754985322667</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -640,22 +608,22 @@
         <v>128</v>
       </c>
       <c r="C9">
-        <v>0.1221172</v>
+        <v>0.1264418</v>
       </c>
       <c r="D9" t="s">
         <v>8</v>
       </c>
       <c r="E9">
-        <v>1.28954E-2</v>
-      </c>
-      <c r="F9" s="3">
-        <v>0.89440144385885034</v>
+        <v>0.0114242</v>
+      </c>
+      <c r="F9">
+        <v>0.909648549767561</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -663,22 +631,22 @@
         <v>16</v>
       </c>
       <c r="C10">
-        <v>3.8020000000000003E-4</v>
+        <v>0.0003684</v>
       </c>
       <c r="D10" t="s">
         <v>9</v>
       </c>
       <c r="E10">
-        <v>3.5809999999999998E-4</v>
-      </c>
-      <c r="F10" s="3">
-        <v>5.8127301420305227E-2</v>
+        <v>0.0003829</v>
+      </c>
+      <c r="F10">
+        <v>-0.03935939196525508</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -686,22 +654,22 @@
         <v>32</v>
       </c>
       <c r="C11">
-        <v>2.4911E-3</v>
+        <v>0.002488</v>
       </c>
       <c r="D11" t="s">
         <v>9</v>
       </c>
       <c r="E11">
-        <v>1.1095E-3</v>
-      </c>
-      <c r="F11" s="3">
-        <v>0.55461442736140665</v>
+        <v>0.0008588000000000001</v>
+      </c>
+      <c r="F11">
+        <v>0.6548231511254019</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -709,22 +677,22 @@
         <v>64</v>
       </c>
       <c r="C12">
-        <v>1.58681E-2</v>
+        <v>0.0161375</v>
       </c>
       <c r="D12" t="s">
         <v>9</v>
       </c>
       <c r="E12">
-        <v>3.0103E-3</v>
-      </c>
-      <c r="F12" s="3">
-        <v>0.8102923475400331</v>
+        <v>0.0027321</v>
+      </c>
+      <c r="F12">
+        <v>0.8306986831913246</v>
       </c>
       <c r="G12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -732,22 +700,22 @@
         <v>128</v>
       </c>
       <c r="C13">
-        <v>0.1031649</v>
+        <v>0.1062307</v>
       </c>
       <c r="D13" t="s">
         <v>9</v>
       </c>
       <c r="E13">
-        <v>1.0972000000000001E-2</v>
-      </c>
-      <c r="F13" s="3">
-        <v>0.89364599781514842</v>
+        <v>0.0102487</v>
+      </c>
+      <c r="F13">
+        <v>0.9035241224994282</v>
       </c>
       <c r="G13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -755,22 +723,22 @@
         <v>16</v>
       </c>
       <c r="C14">
-        <v>5.3509999999999994E-4</v>
+        <v>0.000546</v>
       </c>
       <c r="D14" t="s">
         <v>10</v>
       </c>
       <c r="E14">
-        <v>4.4230000000000002E-4</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0.17342552793870289</v>
+        <v>0.0003426999999999999</v>
+      </c>
+      <c r="F14">
+        <v>0.3723443223443226</v>
       </c>
       <c r="G14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -778,22 +746,22 @@
         <v>32</v>
       </c>
       <c r="C15">
-        <v>3.6208E-3</v>
+        <v>0.003684000000000001</v>
       </c>
       <c r="D15" t="s">
         <v>10</v>
       </c>
       <c r="E15">
-        <v>1.0345E-3</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0.71428965974370295</v>
+        <v>0.0007721000000000001</v>
+      </c>
+      <c r="F15">
+        <v>0.7904180238870794</v>
       </c>
       <c r="G15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -801,22 +769,22 @@
         <v>64</v>
       </c>
       <c r="C16">
-        <v>2.8796100000000002E-2</v>
+        <v>0.030357</v>
       </c>
       <c r="D16" t="s">
         <v>10</v>
       </c>
       <c r="E16">
-        <v>3.0974000000000002E-3</v>
-      </c>
-      <c r="F16" s="3">
-        <v>0.89243682304200911</v>
+        <v>0.0022251</v>
+      </c>
+      <c r="F16">
+        <v>0.9267022433046743</v>
       </c>
       <c r="G16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -824,22 +792,22 @@
         <v>128</v>
       </c>
       <c r="C17">
-        <v>0.2103159</v>
+        <v>0.2180022</v>
       </c>
       <c r="D17" t="s">
         <v>10</v>
       </c>
       <c r="E17">
-        <v>1.11757E-2</v>
-      </c>
-      <c r="F17" s="3">
-        <v>0.94686231521249697</v>
+        <v>0.007606700000000001</v>
+      </c>
+      <c r="F17">
+        <v>0.9651072328627877</v>
       </c>
       <c r="G17" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -847,22 +815,22 @@
         <v>16</v>
       </c>
       <c r="C18">
-        <v>7.6530000000000001E-4</v>
+        <v>0.0007156</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
       </c>
       <c r="E18">
-        <v>4.5429999999999998E-4</v>
-      </c>
-      <c r="F18" s="3">
-        <v>0.40637658434600821</v>
+        <v>0.0003775</v>
+      </c>
+      <c r="F18">
+        <v>0.4724706539966462</v>
       </c>
       <c r="G18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -870,22 +838,22 @@
         <v>32</v>
       </c>
       <c r="C19">
-        <v>5.5338999999999996E-3</v>
+        <v>0.0055638</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
       </c>
       <c r="E19">
-        <v>2.0276999999999999E-3</v>
-      </c>
-      <c r="F19" s="3">
-        <v>0.63358571712535461</v>
+        <v>0.0011277</v>
+      </c>
+      <c r="F19">
+        <v>0.7973147848592689</v>
       </c>
       <c r="G19" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -893,22 +861,22 @@
         <v>64</v>
       </c>
       <c r="C20">
-        <v>4.73926E-2</v>
+        <v>0.0476005</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
       </c>
       <c r="E20">
-        <v>6.6388000000000003E-3</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0.85991905909361377</v>
+        <v>0.0037401</v>
+      </c>
+      <c r="F20">
+        <v>0.9214272959317653</v>
       </c>
       <c r="G20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -916,19 +884,19 @@
         <v>128</v>
       </c>
       <c r="C21">
-        <v>0.32045699999999988</v>
+        <v>0.3275252</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
       </c>
       <c r="E21">
-        <v>2.44447E-2</v>
-      </c>
-      <c r="F21" s="3">
-        <v>0.92371925094474461</v>
+        <v>0.0138309</v>
+      </c>
+      <c r="F21">
+        <v>0.9577714936133159</v>
       </c>
       <c r="G21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Vertical/perbandingan_Waktu Pencarian.xlsx
+++ b/Excel/Vertical/perbandingan_Waktu Pencarian.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="14">
   <si>
     <t>Kombinasi</t>
   </si>
@@ -22,7 +22,7 @@
     <t>Ukuran</t>
   </si>
   <si>
-    <t>Nilai</t>
+    <t>value</t>
   </si>
   <si>
     <t>Map</t>
@@ -53,6 +53,9 @@
   </si>
   <si>
     <t>Tetap</t>
+  </si>
+  <si>
+    <t>Naik</t>
   </si>
 </sst>
 </file>
@@ -444,11 +447,17 @@
         <v>16</v>
       </c>
       <c r="C2">
-        <v>0.0004758999999999999</v>
+        <v>0.0004822</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
       </c>
+      <c r="E2">
+        <v>0.0004822</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
       <c r="G2" t="s">
         <v>12</v>
       </c>
@@ -461,11 +470,17 @@
         <v>32</v>
       </c>
       <c r="C3">
-        <v>0.0035812</v>
+        <v>0.0034743</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
       </c>
+      <c r="E3">
+        <v>0.0034743</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
       <c r="G3" t="s">
         <v>12</v>
       </c>
@@ -478,11 +493,17 @@
         <v>64</v>
       </c>
       <c r="C4">
-        <v>0.0251143</v>
+        <v>0.025808</v>
       </c>
       <c r="D4" t="s">
         <v>3</v>
       </c>
+      <c r="E4">
+        <v>0.025808</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
       <c r="G4" t="s">
         <v>12</v>
       </c>
@@ -495,11 +516,17 @@
         <v>128</v>
       </c>
       <c r="C5">
-        <v>0.1618182</v>
+        <v>0.15967</v>
       </c>
       <c r="D5" t="s">
         <v>3</v>
       </c>
+      <c r="E5">
+        <v>0.15967</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
       <c r="G5" t="s">
         <v>12</v>
       </c>
@@ -512,13 +539,19 @@
         <v>16</v>
       </c>
       <c r="C6">
-        <v>0.0005007</v>
+        <v>0.0005046</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
       </c>
+      <c r="E6">
+        <v>0.0004101</v>
+      </c>
+      <c r="F6">
+        <v>0.1872770511296077</v>
+      </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -529,13 +562,19 @@
         <v>32</v>
       </c>
       <c r="C7">
-        <v>0.0030011</v>
+        <v>0.0029849</v>
       </c>
       <c r="D7" t="s">
         <v>8</v>
       </c>
+      <c r="E7">
+        <v>0.0013158</v>
+      </c>
+      <c r="F7">
+        <v>0.5591812121009079</v>
+      </c>
       <c r="G7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -546,13 +585,19 @@
         <v>64</v>
       </c>
       <c r="C8">
-        <v>0.020182</v>
+        <v>0.0196066</v>
       </c>
       <c r="D8" t="s">
         <v>8</v>
       </c>
+      <c r="E8">
+        <v>0.005923699999999999</v>
+      </c>
+      <c r="F8">
+        <v>0.697872145093999</v>
+      </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -563,13 +608,19 @@
         <v>128</v>
       </c>
       <c r="C9">
-        <v>0.130394</v>
+        <v>0.1302875</v>
       </c>
       <c r="D9" t="s">
         <v>8</v>
       </c>
+      <c r="E9">
+        <v>0.0429991</v>
+      </c>
+      <c r="F9">
+        <v>0.6699675717163964</v>
+      </c>
       <c r="G9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -580,13 +631,19 @@
         <v>16</v>
       </c>
       <c r="C10">
-        <v>0.0008935999999999999</v>
+        <v>0.000411</v>
       </c>
       <c r="D10" t="s">
         <v>9</v>
       </c>
+      <c r="E10">
+        <v>0.0003179</v>
+      </c>
+      <c r="F10">
+        <v>0.2265206812652069</v>
+      </c>
       <c r="G10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -597,13 +654,19 @@
         <v>32</v>
       </c>
       <c r="C11">
-        <v>0.0025451</v>
+        <v>0.0025615</v>
       </c>
       <c r="D11" t="s">
         <v>9</v>
       </c>
+      <c r="E11">
+        <v>0.0018366</v>
+      </c>
+      <c r="F11">
+        <v>0.2829982432168651</v>
+      </c>
       <c r="G11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -614,13 +677,19 @@
         <v>64</v>
       </c>
       <c r="C12">
-        <v>0.0169725</v>
+        <v>0.0168613</v>
       </c>
       <c r="D12" t="s">
         <v>9</v>
       </c>
+      <c r="E12">
+        <v>0.0129962</v>
+      </c>
+      <c r="F12">
+        <v>0.2292290630022596</v>
+      </c>
       <c r="G12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -631,13 +700,19 @@
         <v>128</v>
       </c>
       <c r="C13">
-        <v>0.1116386</v>
+        <v>0.1104541</v>
       </c>
       <c r="D13" t="s">
         <v>9</v>
       </c>
+      <c r="E13">
+        <v>0.08562030000000001</v>
+      </c>
+      <c r="F13">
+        <v>0.2248336639382331</v>
+      </c>
       <c r="G13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -648,13 +723,19 @@
         <v>16</v>
       </c>
       <c r="C14">
-        <v>0.0005920999999999999</v>
+        <v>0.0006736</v>
       </c>
       <c r="D14" t="s">
         <v>10</v>
       </c>
+      <c r="E14">
+        <v>0.0003319</v>
+      </c>
+      <c r="F14">
+        <v>0.5072743467933492</v>
+      </c>
       <c r="G14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -665,13 +746,19 @@
         <v>32</v>
       </c>
       <c r="C15">
-        <v>0.0038504</v>
+        <v>0.003875100000000001</v>
       </c>
       <c r="D15" t="s">
         <v>10</v>
       </c>
+      <c r="E15">
+        <v>0.0010794</v>
+      </c>
+      <c r="F15">
+        <v>0.7214523496167841</v>
+      </c>
       <c r="G15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -682,13 +769,19 @@
         <v>64</v>
       </c>
       <c r="C16">
-        <v>0.029364</v>
+        <v>0.0296328</v>
       </c>
       <c r="D16" t="s">
         <v>10</v>
       </c>
+      <c r="E16">
+        <v>0.0036981</v>
+      </c>
+      <c r="F16">
+        <v>0.8752024783348182</v>
+      </c>
       <c r="G16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -699,13 +792,19 @@
         <v>128</v>
       </c>
       <c r="C17">
-        <v>0.2250544</v>
+        <v>0.2242598</v>
       </c>
       <c r="D17" t="s">
         <v>10</v>
       </c>
+      <c r="E17">
+        <v>0.0150779</v>
+      </c>
+      <c r="F17">
+        <v>0.9327659259483866</v>
+      </c>
       <c r="G17" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -716,13 +815,19 @@
         <v>16</v>
       </c>
       <c r="C18">
-        <v>0.0010808</v>
+        <v>0.0007793</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
       </c>
+      <c r="E18">
+        <v>0.0005113</v>
+      </c>
+      <c r="F18">
+        <v>0.3438983703323495</v>
+      </c>
       <c r="G18" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -733,13 +838,19 @@
         <v>32</v>
       </c>
       <c r="C19">
-        <v>0.0058226</v>
+        <v>0.0057743</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
       </c>
+      <c r="E19">
+        <v>0.0035126</v>
+      </c>
+      <c r="F19">
+        <v>0.391683840465511</v>
+      </c>
       <c r="G19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -750,13 +861,19 @@
         <v>64</v>
       </c>
       <c r="C20">
-        <v>0.0493748</v>
+        <v>0.0501117</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
       </c>
+      <c r="E20">
+        <v>0.0248513</v>
+      </c>
+      <c r="F20">
+        <v>0.5040818810776725</v>
+      </c>
       <c r="G20" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -767,13 +884,19 @@
         <v>128</v>
       </c>
       <c r="C21">
-        <v>0.3418717999999999</v>
+        <v>0.340181</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
       </c>
+      <c r="E21">
+        <v>0.1598635</v>
+      </c>
+      <c r="F21">
+        <v>0.5300634074213434</v>
+      </c>
       <c r="G21" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Vertical/perbandingan_Waktu Pencarian.xlsx
+++ b/Excel/Vertical/perbandingan_Waktu Pencarian.xlsx
@@ -447,13 +447,13 @@
         <v>16</v>
       </c>
       <c r="C2">
-        <v>0.0004822</v>
+        <v>0.0005032000000000001</v>
       </c>
       <c r="D2" t="s">
         <v>3</v>
       </c>
       <c r="E2">
-        <v>0.0004822</v>
+        <v>0.0005032000000000001</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -470,13 +470,13 @@
         <v>32</v>
       </c>
       <c r="C3">
-        <v>0.0034743</v>
+        <v>0.003523399999999999</v>
       </c>
       <c r="D3" t="s">
         <v>3</v>
       </c>
       <c r="E3">
-        <v>0.0034743</v>
+        <v>0.003523399999999999</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -493,13 +493,13 @@
         <v>64</v>
       </c>
       <c r="C4">
-        <v>0.025808</v>
+        <v>0.0245314</v>
       </c>
       <c r="D4" t="s">
         <v>3</v>
       </c>
       <c r="E4">
-        <v>0.025808</v>
+        <v>0.0245314</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -516,13 +516,13 @@
         <v>128</v>
       </c>
       <c r="C5">
-        <v>0.15967</v>
+        <v>0.1620138</v>
       </c>
       <c r="D5" t="s">
         <v>3</v>
       </c>
       <c r="E5">
-        <v>0.15967</v>
+        <v>0.1620138</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -539,16 +539,16 @@
         <v>16</v>
       </c>
       <c r="C6">
-        <v>0.0005046</v>
+        <v>0.0004917</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
       </c>
       <c r="E6">
-        <v>0.0004101</v>
+        <v>0.0001963</v>
       </c>
       <c r="F6">
-        <v>0.1872770511296077</v>
+        <v>0.6007728289607484</v>
       </c>
       <c r="G6" t="s">
         <v>13</v>
@@ -562,16 +562,16 @@
         <v>32</v>
       </c>
       <c r="C7">
-        <v>0.0029849</v>
+        <v>0.0029884</v>
       </c>
       <c r="D7" t="s">
         <v>8</v>
       </c>
       <c r="E7">
-        <v>0.0013158</v>
+        <v>0.0006369999999999999</v>
       </c>
       <c r="F7">
-        <v>0.5591812121009079</v>
+        <v>0.7868424575023424</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
@@ -585,16 +585,16 @@
         <v>64</v>
       </c>
       <c r="C8">
-        <v>0.0196066</v>
+        <v>0.0202147</v>
       </c>
       <c r="D8" t="s">
         <v>8</v>
       </c>
       <c r="E8">
-        <v>0.005923699999999999</v>
+        <v>0.0020404</v>
       </c>
       <c r="F8">
-        <v>0.697872145093999</v>
+        <v>0.8990635527611094</v>
       </c>
       <c r="G8" t="s">
         <v>13</v>
@@ -608,16 +608,16 @@
         <v>128</v>
       </c>
       <c r="C9">
-        <v>0.1302875</v>
+        <v>0.1326106</v>
       </c>
       <c r="D9" t="s">
         <v>8</v>
       </c>
       <c r="E9">
-        <v>0.0429991</v>
+        <v>0.0074792</v>
       </c>
       <c r="F9">
-        <v>0.6699675717163964</v>
+        <v>0.943600285346722</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
@@ -631,16 +631,16 @@
         <v>16</v>
       </c>
       <c r="C10">
-        <v>0.000411</v>
+        <v>0.0003857</v>
       </c>
       <c r="D10" t="s">
         <v>9</v>
       </c>
       <c r="E10">
-        <v>0.0003179</v>
+        <v>0.0003287</v>
       </c>
       <c r="F10">
-        <v>0.2265206812652069</v>
+        <v>0.147783251231527</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
@@ -654,16 +654,16 @@
         <v>32</v>
       </c>
       <c r="C11">
-        <v>0.0025615</v>
+        <v>0.0025202</v>
       </c>
       <c r="D11" t="s">
         <v>9</v>
       </c>
       <c r="E11">
-        <v>0.0018366</v>
+        <v>0.0018679</v>
       </c>
       <c r="F11">
-        <v>0.2829982432168651</v>
+        <v>0.2588286643917149</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
@@ -677,16 +677,16 @@
         <v>64</v>
       </c>
       <c r="C12">
-        <v>0.0168613</v>
+        <v>0.0171838</v>
       </c>
       <c r="D12" t="s">
         <v>9</v>
       </c>
       <c r="E12">
-        <v>0.0129962</v>
+        <v>0.0127819</v>
       </c>
       <c r="F12">
-        <v>0.2292290630022596</v>
+        <v>0.2561656909414681</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
@@ -700,16 +700,16 @@
         <v>128</v>
       </c>
       <c r="C13">
-        <v>0.1104541</v>
+        <v>0.1113246</v>
       </c>
       <c r="D13" t="s">
         <v>9</v>
       </c>
       <c r="E13">
-        <v>0.08562030000000001</v>
+        <v>0.08665039999999999</v>
       </c>
       <c r="F13">
-        <v>0.2248336639382331</v>
+        <v>0.2216419371818988</v>
       </c>
       <c r="G13" t="s">
         <v>13</v>
@@ -723,16 +723,16 @@
         <v>16</v>
       </c>
       <c r="C14">
-        <v>0.0006736</v>
+        <v>0.0005730000000000001</v>
       </c>
       <c r="D14" t="s">
         <v>10</v>
       </c>
       <c r="E14">
-        <v>0.0003319</v>
+        <v>0.0003375</v>
       </c>
       <c r="F14">
-        <v>0.5072743467933492</v>
+        <v>0.4109947643979058</v>
       </c>
       <c r="G14" t="s">
         <v>13</v>
@@ -746,16 +746,16 @@
         <v>32</v>
       </c>
       <c r="C15">
-        <v>0.003875100000000001</v>
+        <v>0.0039611</v>
       </c>
       <c r="D15" t="s">
         <v>10</v>
       </c>
       <c r="E15">
-        <v>0.0010794</v>
+        <v>0.0011568</v>
       </c>
       <c r="F15">
-        <v>0.7214523496167841</v>
+        <v>0.7079599101259751</v>
       </c>
       <c r="G15" t="s">
         <v>13</v>
@@ -769,16 +769,16 @@
         <v>64</v>
       </c>
       <c r="C16">
-        <v>0.0296328</v>
+        <v>0.0298233</v>
       </c>
       <c r="D16" t="s">
         <v>10</v>
       </c>
       <c r="E16">
-        <v>0.0036981</v>
+        <v>0.0036926</v>
       </c>
       <c r="F16">
-        <v>0.8752024783348182</v>
+        <v>0.8761840574316054</v>
       </c>
       <c r="G16" t="s">
         <v>13</v>
@@ -792,16 +792,16 @@
         <v>128</v>
       </c>
       <c r="C17">
-        <v>0.2242598</v>
+        <v>0.2253527</v>
       </c>
       <c r="D17" t="s">
         <v>10</v>
       </c>
       <c r="E17">
-        <v>0.0150779</v>
+        <v>0.015071</v>
       </c>
       <c r="F17">
-        <v>0.9327659259483866</v>
+        <v>0.933122611799193</v>
       </c>
       <c r="G17" t="s">
         <v>13</v>
@@ -815,16 +815,16 @@
         <v>16</v>
       </c>
       <c r="C18">
-        <v>0.0007793</v>
+        <v>0.0014131</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
       </c>
       <c r="E18">
-        <v>0.0005113</v>
+        <v>0.0004804</v>
       </c>
       <c r="F18">
-        <v>0.3438983703323495</v>
+        <v>0.6600382138560612</v>
       </c>
       <c r="G18" t="s">
         <v>13</v>
@@ -838,16 +838,16 @@
         <v>32</v>
       </c>
       <c r="C19">
-        <v>0.0057743</v>
+        <v>0.005987899999999999</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
       </c>
       <c r="E19">
-        <v>0.0035126</v>
+        <v>0.0034676</v>
       </c>
       <c r="F19">
-        <v>0.391683840465511</v>
+        <v>0.4208988126054208</v>
       </c>
       <c r="G19" t="s">
         <v>13</v>
@@ -861,16 +861,16 @@
         <v>64</v>
       </c>
       <c r="C20">
-        <v>0.0501117</v>
+        <v>0.0491155</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
       </c>
       <c r="E20">
-        <v>0.0248513</v>
+        <v>0.0243821</v>
       </c>
       <c r="F20">
-        <v>0.5040818810776725</v>
+        <v>0.5035762641121438</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
@@ -884,16 +884,16 @@
         <v>128</v>
       </c>
       <c r="C21">
-        <v>0.340181</v>
+        <v>0.3437210000000001</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
       </c>
       <c r="E21">
-        <v>0.1598635</v>
+        <v>0.1615691</v>
       </c>
       <c r="F21">
-        <v>0.5300634074213434</v>
+        <v>0.5299411441256137</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
